--- a/MappingGuides/mapping/guides/MappingGuide_PDS001MI_Product.xlsx
+++ b/MappingGuides/mapping/guides/MappingGuide_PDS001MI_Product.xlsx
@@ -935,12 +935,7 @@
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.</t>
-        </is>
-      </c>
+      <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1047,14 +1042,7 @@
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).</t>
-        </is>
-      </c>
+      <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1165,13 +1153,7 @@
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr"/>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product number.
-For a product structure with a product structure class type of 00-'Standard' (i.e. discrete items), the product number is the same as the item number manufactured (the output from the manufacturing order) and is always used together with structures to describe what a product consists of and how it is manufactured.
-There are scenarios where each process is created as a product number on (PDS001) to serve as a placeholder for product structure class types other than 00-'Standard'. In the cases where the product structure class type is Formula product structure, Routing product structure, Bulk item product structure, Packaging material product structure, or Packaged item product structure, the Product number field is used to identify a process required for the manufacture of the ultimate product number.</t>
-        </is>
-      </c>
+      <c r="AA5" s="2" t="inlineStr"/>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1278,11 +1260,7 @@
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr"/>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a product structure type. You can define more than one product structure per product and facility.</t>
-        </is>
-      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -1479,11 +1457,7 @@
       <c r="X8" s="2" t="inlineStr"/>
       <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr"/>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates an optional text of at most 30 characters.</t>
-        </is>
-      </c>
+      <c r="AA8" s="2" t="inlineStr"/>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
@@ -1566,12 +1540,7 @@
       <c r="X9" s="2" t="inlineStr"/>
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr"/>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a unique user ID.
-The ID can be used for selection and sorting.</t>
-        </is>
-      </c>
+      <c r="AA9" s="2" t="inlineStr"/>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
@@ -1666,14 +1635,7 @@
       <c r="X10" s="2" t="inlineStr"/>
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the normal order quantity of each item/warehouse, that is the quantity that should be ordered when a requirement arises. The quantity often refers to the economical quantity.
-Order quantity is always expressed in the basic U/M of each item.
-The order quantity method determines if the quantity has been entered manually or was calculated according to a predefined rule.
-Use the order quantity to create a batch of planning in requirements calculations, to suggest quantities in planned orders and even to distribute setup costs during estimation, for example.</t>
-        </is>
-      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr"/>
@@ -1760,12 +1722,7 @@
       <c r="X11" s="2" t="inlineStr"/>
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a unique ID for the drawing used in designing the item.
-The drawing number is set per item and can also be used as a search key in both the item file and product structures.</t>
-        </is>
-      </c>
+      <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr"/>
@@ -1852,11 +1809,7 @@
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many put-away cards that should be printed for each product and order.</t>
-        </is>
-      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr"/>
@@ -1947,11 +1900,7 @@
       <c r="X13" s="2" t="inlineStr"/>
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many material requisitions that are normally printed for each material in connection with an order.</t>
-        </is>
-      </c>
+      <c r="AA13" s="2" t="inlineStr"/>
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr"/>
@@ -2042,12 +1991,7 @@
       <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of labor tickets that should be printed for each operation included in a product.
-This quantity is multiplied by the labor ticket multiplier for each operation, so each user may determine the number of labor tickets for an operation.</t>
-        </is>
-      </c>
+      <c r="AA14" s="2" t="inlineStr"/>
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr"/>
@@ -2138,11 +2082,7 @@
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many shop traveler cards should normally be printed for each order.</t>
-        </is>
-      </c>
+      <c r="AA15" s="2" t="inlineStr"/>
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr"/>
@@ -2233,11 +2173,7 @@
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many routing cards per operation that are normally printed.</t>
-        </is>
-      </c>
+      <c r="AA16" s="2" t="inlineStr"/>
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr"/>
@@ -2320,11 +2256,7 @@
       <c r="X17" s="2" t="inlineStr"/>
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many picking lists that are normally printed for each order.</t>
-        </is>
-      </c>
+      <c r="AA17" s="2" t="inlineStr"/>
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr"/>
@@ -2411,11 +2343,7 @@
       <c r="X18" s="2" t="inlineStr"/>
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of design documents which normally should be printed for each item and order.</t>
-        </is>
-      </c>
+      <c r="AA18" s="2" t="inlineStr"/>
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr"/>
@@ -2599,18 +2527,8 @@
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether to recalculate quantities used in connection with a change of batch sizes.</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0: No.
-1: Yes - all components and operations are included are recalculated.
-2: Yes - only yield components are recalculated.</t>
-        </is>
-      </c>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr"/>
       <c r="AE20" s="2" t="inlineStr"/>
@@ -2704,12 +2622,7 @@
       <c r="X21" s="2" t="inlineStr"/>
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr"/>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product's theoretical yield, expressed as a percentage to two decimal places. You can specify either the yield percentage or the yield quantity manually. If you leave this value blank, it will be calculated automatically.
-The yield is calculated as the quotient between the yield quantity and the batch quantity.</t>
-        </is>
-      </c>
+      <c r="AA21" s="2" t="inlineStr"/>
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr"/>
@@ -2792,18 +2705,8 @@
       <c r="X22" s="2" t="inlineStr"/>
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how product configuration should be performed.</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0: The product's configuration is not dynamic
-1: The configuration is multi-level dynamic
-2: The configuration is one-level dynamic.</t>
-        </is>
-      </c>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr"/>
       <c r="AE22" s="2" t="inlineStr"/>
@@ -2889,12 +2792,7 @@
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if the start date should be the same for all batches created for the same order. This code is only used when the number of batches is specified when entering a new order.
-Production should be planned by using forward scheduling, in other words, by using the start date. If you have created a bottleneck in the routing list, all batches will be planned automatically as close together as possible.</t>
-        </is>
-      </c>
+      <c r="AA23" s="2" t="inlineStr"/>
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr"/>
@@ -2977,12 +2875,7 @@
       <c r="X24" s="2" t="inlineStr"/>
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to order a product in batches.
-If the check box is not selected the product will be ordered in units.</t>
-        </is>
-      </c>
+      <c r="AA24" s="2" t="inlineStr"/>
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr"/>
@@ -3069,12 +2962,7 @@
       <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the current lead time on this level based on the operations to be performed, regardless of how lead time is determined/calculated.
-When the calculation is done automatically, it has been based on the following information: order quantity, setup time, run time and queue time compared to the lead time capacity.</t>
-        </is>
-      </c>
+      <c r="AA25" s="2" t="inlineStr"/>
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr"/>
@@ -3165,12 +3053,7 @@
       <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr"/>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how to calculate the total production lead time or manufacturing time for a product, considering required production of semi-finished products. Required production means that consideration must be given to explosion and/or fictitious items. The lead time is calculated considering the order quantity, setup and run times as well as the queue times between operations.
-After the calculation is made, the lead time is updated in the item/warehouse file.</t>
-        </is>
-      </c>
+      <c r="AA26" s="2" t="inlineStr"/>
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr"/>
@@ -3253,12 +3136,7 @@
       <c r="X27" s="2" t="inlineStr"/>
       <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr"/>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the structure complexity in the form of a multiplier.
-The structure complexity can function as a cost driver in the product costing. A costing price can be specified for each multiplication unit. This is then multiplied by the structure complexity to obtain a calculated cost.</t>
-        </is>
-      </c>
+      <c r="AA27" s="2" t="inlineStr"/>
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr"/>
@@ -3341,18 +3219,8 @@
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr"/>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if and how alternate routings are to be handled for a product.</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0: Alternate routings do not exist.
-1: The alternate ID for the routing must be entered manually.
-2: The alternate ID for the routing will be selected automatically.</t>
-        </is>
-      </c>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr"/>
       <c r="AE28" s="2" t="inlineStr"/>
@@ -3434,12 +3302,7 @@
       <c r="X29" s="2" t="inlineStr"/>
       <c r="Y29" s="2" t="inlineStr"/>
       <c r="Z29" s="2" t="inlineStr"/>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the total number of components in a bill of material.
-This number is automatically calculated for each product.</t>
-        </is>
-      </c>
+      <c r="AA29" s="2" t="inlineStr"/>
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr"/>
@@ -3526,14 +3389,7 @@
       <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="inlineStr"/>
       <c r="Z30" s="2" t="inlineStr"/>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of operations to be performed.
-This number includes operations which are performed in work centers with planning policy 1 or 2.
-Subcontract operations are accounted for separately.
-The number of operations is calculated automatically per product.</t>
-        </is>
-      </c>
+      <c r="AA30" s="2" t="inlineStr"/>
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr"/>
@@ -3620,12 +3476,7 @@
       <c r="X31" s="2" t="inlineStr"/>
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr"/>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many operations are subcontracted. In other words, they are performed in work centers with planning type 3.
-The number of subcontract operations is calculated automatically for each product.</t>
-        </is>
-      </c>
+      <c r="AA31" s="2" t="inlineStr"/>
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr"/>
@@ -3708,11 +3559,7 @@
       <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr"/>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of phantom materials which are calculated automatically for each product. It also displays how much of the material included are phantom items, that is, item type category 2.</t>
-        </is>
-      </c>
+      <c r="AA32" s="2" t="inlineStr"/>
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr"/>
@@ -3799,12 +3646,7 @@
       <c r="X33" s="2" t="inlineStr"/>
       <c r="Y33" s="2" t="inlineStr"/>
       <c r="Z33" s="2" t="inlineStr"/>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates, for each product, how many of the materials are included in the yield calculation.
-The information is calculated automatically in connection with lead time calculation and cannot be changed manually.</t>
-        </is>
-      </c>
+      <c r="AA33" s="2" t="inlineStr"/>
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr"/>
@@ -3891,12 +3733,7 @@
       <c r="X34" s="2" t="inlineStr"/>
       <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr"/>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product's batch quantity expressed in the unit specified for the product. It represents the gross amount used by the production process, while the yield quantity represents the net outcome of the process.
-The theoretical yield is calculated as the quotient between the yield quantity and the batch quantity. The batch quantity is always calculated automatically as the sum of the included components usage, considering the specified yield per operation. Consideration is even given to the scrap, setup wastage and pure material wastage.</t>
-        </is>
-      </c>
+      <c r="AA34" s="2" t="inlineStr"/>
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr"/>
@@ -3983,15 +3820,7 @@
       <c r="X35" s="2" t="inlineStr"/>
       <c r="Y35" s="2" t="inlineStr"/>
       <c r="Z35" s="2" t="inlineStr"/>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the lowest level (low level code) at which a material or a semi-finished product may be used in product structures and distribution network.
-The lowest level determines the order for product costing and requirements calculations. It may even be used to describe the relative levels for different documents in a document structure.
-The level is assigned automatically and cannot be changed manually.
-The lower the level in the product structure, the higher value.
-Finished products that are not used in other products are always in the highest level and have level 00.</t>
-        </is>
-      </c>
+      <c r="AA35" s="2" t="inlineStr"/>
       <c r="AB35" s="2" t="inlineStr"/>
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr"/>
@@ -4074,12 +3903,7 @@
       <c r="X36" s="2" t="inlineStr"/>
       <c r="Y36" s="2" t="inlineStr"/>
       <c r="Z36" s="2" t="inlineStr"/>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many semi-manufactured products are included in the product.
-A semi-manufactured product is an item with planning method 3. This means that semi-manufactured products are to be manufactured at the same time as the product being manufactured.</t>
-        </is>
-      </c>
+      <c r="AA36" s="2" t="inlineStr"/>
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr"/>
@@ -4166,12 +3990,7 @@
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr"/>
       <c r="Z37" s="2" t="inlineStr"/>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates accumulated scrap percentage.
-Accumulated scrap percentage is calculated automatically per product. The calculation is made through the operation chain of each product and is based on the scrap percentages that have been entered on its operations.</t>
-        </is>
-      </c>
+      <c r="AA37" s="2" t="inlineStr"/>
       <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr"/>
@@ -4348,18 +4167,8 @@
       <c r="X39" s="2" t="inlineStr"/>
       <c r="Y39" s="2" t="inlineStr"/>
       <c r="Z39" s="2" t="inlineStr"/>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the sales price for the kit item and the detail lines are calculated.</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>1: The sales amount of the kit item is distributed among the detail lines. The distribution basis is the cost of the detail lines. See note 1.
-2: The sales amount of the kit item is distributed among the detail lines. The distribution basis is the line amount of the detail lines calculated with the sales price according to the price hierarchy. See note 2.
-3: The sales price of the kit item is the sum of the values of the detail lines. See note 3.</t>
-        </is>
-      </c>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr"/>
       <c r="AE39" s="2" t="inlineStr"/>
@@ -4441,17 +4250,8 @@
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
       <c r="Z40" s="2" t="inlineStr"/>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the inventory reservation should be performed.</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>1: At kit number level, provided that the item has been entered as accounted in the item file.
-2: At material number level, provided that the items included are entered as accounted in the item file.</t>
-        </is>
-      </c>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr"/>
       <c r="AE40" s="2" t="inlineStr"/>
@@ -4626,12 +4426,7 @@
       <c r="X42" s="2" t="inlineStr"/>
       <c r="Y42" s="2" t="inlineStr"/>
       <c r="Z42" s="2" t="inlineStr"/>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if the cost price from each detail line should be totaled to kit line, included quantities considered.
-If the check box is not selected the cost price must be entered manually if the order type indicates this.</t>
-        </is>
-      </c>
+      <c r="AA42" s="2" t="inlineStr"/>
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr"/>
@@ -4714,17 +4509,8 @@
       <c r="X43" s="2" t="inlineStr"/>
       <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr"/>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates what is printed on the CO confirmation and the CO invoice.</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>1: Kit line and detail lines are printed
-2: Only kit line is printed.</t>
-        </is>
-      </c>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr"/>
       <c r="AE43" s="2" t="inlineStr"/>
@@ -4806,11 +4592,7 @@
       <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr"/>
       <c r="Z44" s="2" t="inlineStr"/>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of the routing to be used as a standard routing.</t>
-        </is>
-      </c>
+      <c r="AA44" s="2" t="inlineStr"/>
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr"/>
@@ -4893,35 +4675,8 @@
       <c r="X45" s="2" t="inlineStr"/>
       <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a parameter used in M3 SWB with different meanings for pegged and non-pegged orders.</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0: The global parameter set in the Automatic Simulation - Advanced panel is used.
-1: No pull-up. The order is only forward scheduled.
-2: Pull-up to last operation. The lead time of the order is minimized.
-3: Same as 2.
-4: Same as 2.
-0: The global parameter in the Automatic Simulation - Advanced panel is used.
-1: No pull-up. The order is only forward scheduled.
-2: Pull-up to last operation. The lead time of the order is minimized.
-3: Pull-up to finite need date of the parent order.
-4: Same as 3.
-0: The general parameter Pull-up Delayed End Item Orders in the Automatic Simulation - Advanced panel is used.
-1: No pull-up. The order is only forward scheduled.
-2: Pull-up to last operation.
-3: Same as 2.
-4: Same as 2.
-0: The general parameter Pull-up Delayed Component Orders in the Automatic Simulation - Advanced panel is used.
-1: No pull-up. The order is only forward scheduled.
-2: Pull-up to last operation.
-3: Pull-up to finite need date of the parent order.
-4: Same as 3.</t>
-        </is>
-      </c>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr"/>
       <c r="AE45" s="2" t="inlineStr"/>
@@ -5003,35 +4758,8 @@
       <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr"/>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a parameter used in M3 SWB with different meanings for pegged and non-pegged orders.</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr">
-        <is>
-          <t>0: The global parameter set in the Automatic Simulation - Advanced panel is used.
-1: No pull-up. The order is only forward scheduled.
-2: Pull-up to last operation. The lead time of the order is minimized.
-3: Pull-up to due date.
-4: Same as 3.
-0: The global parameter in the Automatic Simulation - Advanced panel is used.
-1: No pull-up. The order is only forward scheduled.
-2: Pull-up to last operation. The lead time of the order itself is minimized.
-3: Pull-up to finite need date of the parent order.
-4: Pull-up to finite need date of the parent order, but not later than the infinite need date of the parent order.
-0: The global parameter in the Automatic Simulation - Advanced panel is used.
-1: No pull-up. The order is only forward scheduled.
-2: Pull-up to last operation.
-3: Pull-up to due date.
-4: Same as 3.
-0: The global parameter in the Automatic Simulation - Advanced panel is used.
-1: No pull-up. The order is only forward scheduled.
-2: Pull-up to last operation.
-3: Pull-up to finite need date of the parent order.
-4: Pull-up to finite need date of the parent order, but not later than the infinite need date of the parent order.</t>
-        </is>
-      </c>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr"/>
       <c r="AE46" s="2" t="inlineStr"/>
@@ -5113,12 +4841,7 @@
       <c r="X47" s="2" t="inlineStr"/>
       <c r="Y47" s="2" t="inlineStr"/>
       <c r="Z47" s="2" t="inlineStr"/>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the BoM is based on percentages or quantity.
-If this parameter is 1, then the Quantity relation parameter in (PDS002) is defaulted as 2.</t>
-        </is>
-      </c>
+      <c r="AA47" s="2" t="inlineStr"/>
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr"/>
@@ -5201,11 +4924,7 @@
       <c r="X48" s="2" t="inlineStr"/>
       <c r="Y48" s="2" t="inlineStr"/>
       <c r="Z48" s="2" t="inlineStr"/>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if any operations for the product are production lot controlled.</t>
-        </is>
-      </c>
+      <c r="AA48" s="2" t="inlineStr"/>
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr"/>
@@ -5288,11 +5007,7 @@
       <c r="X49" s="2" t="inlineStr"/>
       <c r="Y49" s="2" t="inlineStr"/>
       <c r="Z49" s="2" t="inlineStr"/>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of production lot cards that are normally printed for each item and manufacturing order.</t>
-        </is>
-      </c>
+      <c r="AA49" s="2" t="inlineStr"/>
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr"/>
@@ -5367,11 +5082,7 @@
       <c r="X50" s="2" t="inlineStr"/>
       <c r="Y50" s="2" t="inlineStr"/>
       <c r="Z50" s="2" t="inlineStr"/>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the text ID, which identifies comments made. It is updated automatically when entering comments.</t>
-        </is>
-      </c>
+      <c r="AA50" s="2" t="inlineStr"/>
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr"/>
@@ -5446,11 +5157,7 @@
       <c r="X51" s="2" t="inlineStr"/>
       <c r="Y51" s="2" t="inlineStr"/>
       <c r="Z51" s="2" t="inlineStr"/>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to suppress the kit screen during customer order line entry (the H-panel).</t>
-        </is>
-      </c>
+      <c r="AA51" s="2" t="inlineStr"/>
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr"/>
@@ -5525,18 +5232,8 @@
       <c r="X52" s="2" t="inlineStr"/>
       <c r="Y52" s="2" t="inlineStr"/>
       <c r="Z52" s="2" t="inlineStr"/>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the kit information that is to be printed on the purchase order document.</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>0: Only the reservation level is printed
-1: Both reservation level and price level are printed
-2: All levels are always printed</t>
-        </is>
-      </c>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr"/>
       <c r="AE52" s="2" t="inlineStr"/>
@@ -5610,12 +5307,7 @@
       <c r="X53" s="2" t="inlineStr"/>
       <c r="Y53" s="2" t="inlineStr"/>
       <c r="Z53" s="2" t="inlineStr"/>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a user-defined product structure class for the purpose of grouping product structures.
-When defining a product structure class, you may assign a class type, including a blank structure class ('Discrete'), formula product structure, routing product structure, bulk item product structure, packaging material product structure, or packaged item product structure. The assigned type determines how components are assembled in a product structure.</t>
-        </is>
-      </c>
+      <c r="AA53" s="2" t="inlineStr"/>
       <c r="AB53" s="2" t="inlineStr"/>
       <c r="AC53" s="2" t="inlineStr">
         <is>
@@ -5694,13 +5386,7 @@
       <c r="X54" s="2" t="inlineStr"/>
       <c r="Y54" s="2" t="inlineStr"/>
       <c r="Z54" s="2" t="inlineStr"/>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to indicate that the product structure is managed by version. Versions may be applied to product structures that represent manufacturing processes. When the Version management field value = 1 in (CRS008), the Version managed (VRNF) check box may be selected for the desired product structures in (PDS001). If the Version management field value = 2 in (CRS008), the check box is enabled automatically in (PDS001) because version management is mandatory.
-This check box operates independently of the Process manufacturing (PMFL) setting in (CRS008).
-You cannot change this setting on a product structure record after further data setup has been completed.</t>
-        </is>
-      </c>
+      <c r="AA54" s="2" t="inlineStr"/>
       <c r="AB54" s="2" t="inlineStr"/>
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr"/>
@@ -5775,11 +5461,7 @@
       <c r="X55" s="2" t="inlineStr"/>
       <c r="Y55" s="2" t="inlineStr"/>
       <c r="Z55" s="2" t="inlineStr"/>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to indicate whether the product structure has been created through an interface, typically with a product lifecycle management system. This flag is not changeable after creation.</t>
-        </is>
-      </c>
+      <c r="AA55" s="2" t="inlineStr"/>
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr"/>
@@ -5854,13 +5536,7 @@
       <c r="X56" s="2" t="inlineStr"/>
       <c r="Y56" s="2" t="inlineStr"/>
       <c r="Z56" s="2" t="inlineStr"/>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to allow date gaps between material/operation lines having the same sequence/operation number in (PDS002). Any changes resulting in a gap in the date sequence will be kept. If the check box is not selected, the 'To date' will be adjusted to the day before the next 'From date'.
-Note: 
-Overlapping materials and operations are not allowed in the product structure, and the valid 'To date' will therefore be adjusted up to the 'From date' of the next line. For example, if the user adds a material line with the same sequence number and a 'From date' that coincides with the 'To date' of the previous line, the 'To date' of the previous line will be adjusted. When adding a material line with a 'To date' that coincides with the valid date of the next record, this 'To date' will be adjusted.</t>
-        </is>
-      </c>
+      <c r="AA56" s="2" t="inlineStr"/>
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr"/>
@@ -5935,18 +5611,8 @@
       <c r="X57" s="2" t="inlineStr"/>
       <c r="Y57" s="2" t="inlineStr"/>
       <c r="Z57" s="2" t="inlineStr"/>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>The field indicate how backflush issue transactions are created: aggregated or detailed.</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>0: No.
-1: Yes.
-2: Yes, automatically activated at MO closure.</t>
-        </is>
-      </c>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr"/>
       <c r="AE57" s="2" t="inlineStr"/>
